--- a/backend/storage/schema/operations_template.xlsx
+++ b/backend/storage/schema/operations_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/longlh123/Languages/GitHub/IPSOS-FINANCE-PAYMENT/backend/storage/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FECEAF-E1F7-F74F-9D51-E33D0ADC38B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEAECBA-63B1-F24E-A61F-2D1B90FDDA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="3960" windowWidth="29040" windowHeight="17520" xr2:uid="{C9138D76-07EC-41C4-8817-AFCBF30C50C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>field_name</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>target_for_interviewers</t>
+  </si>
+  <si>
+    <t>F2F,CLT,HUT</t>
   </si>
 </sst>
 </file>
@@ -483,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6694FA44-4A7D-4629-A892-7DFDEEB80386}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -495,7 +498,7 @@
     <col min="7" max="7" width="84.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,8 +529,11 @@
       <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -550,8 +556,11 @@
       <c r="I2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -573,8 +582,11 @@
       <c r="I3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -595,6 +607,9 @@
       </c>
       <c r="I4">
         <v>6</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
